--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV16_regime_templates_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV16_regime_templates_data.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-2e29da7b7e67</t>
+          <t>d1-final-57bdbc83894f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,16 +498,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.335809319704331</v>
+        <v>1.334969113657857</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1735395899273336</v>
+        <v>0.1771281425030413</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9070061532873342</v>
+        <v>-0.9030920280545595</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6023427563443309</v>
+        <v>-0.6090052281063398</v>
       </c>
     </row>
     <row r="3">
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.423755184279917</v>
+        <v>1.42233930465182</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.03279832305703111</v>
+        <v>-0.02908114856459194</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6483204569051971</v>
+        <v>-0.644170259866192</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7426364043176887</v>
+        <v>-0.7490878962210363</v>
       </c>
     </row>
     <row r="4">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6339535362107376</v>
+        <v>0.6325744471908278</v>
       </c>
       <c r="C4" t="n">
-        <v>1.062336857247284</v>
+        <v>1.063835444743421</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9723095738421952</v>
+        <v>-0.9690173657198674</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7239808196158252</v>
+        <v>-0.7273925262143814</v>
       </c>
     </row>
     <row r="5">
@@ -555,16 +555,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.2673181213413214</v>
+        <v>-0.1980647397956018</v>
       </c>
       <c r="C5" t="n">
-        <v>1.480121988916043</v>
+        <v>1.450795803592178</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5776199515968532</v>
+        <v>-0.4383851538956044</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6351839159778672</v>
+        <v>-0.8143459099009709</v>
       </c>
     </row>
     <row r="6">
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.580612998283954</v>
+        <v>0.5864695142181653</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.7593228231320349</v>
+        <v>-0.7599771007230918</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9280761572535984</v>
+        <v>-0.9289772284038152</v>
       </c>
       <c r="E6" t="n">
-        <v>1.106785982101679</v>
+        <v>1.102484814908742</v>
       </c>
     </row>
     <row r="7">
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.03888157240041</v>
+        <v>1.04386616431932</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.086659981064276</v>
+        <v>-1.086602970952858</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5838618151827376</v>
+        <v>-0.5822427827427386</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6316402238466023</v>
+        <v>0.6249795893762748</v>
       </c>
     </row>
     <row r="8">
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7403363776459275</v>
+        <v>0.7421978440480835</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6615501633208829</v>
+        <v>0.6614489719394756</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.419137381056833</v>
+        <v>-1.418241755263595</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01725084009002202</v>
+        <v>0.01459493927603462</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.8880840488506314</v>
+        <v>-0.8749464036495195</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2325687185826301</v>
+        <v>-0.2403154172827242</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.314097770167876</v>
+        <v>-0.3240604794323711</v>
       </c>
       <c r="E9" t="n">
-        <v>1.434750537601138</v>
+        <v>1.439322300364614</v>
       </c>
     </row>
     <row r="10">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.167057472882666</v>
+        <v>-1.167279247796931</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1653344419977728</v>
+        <v>0.1658584411076214</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2437580933417366</v>
+        <v>-0.2437787438405123</v>
       </c>
       <c r="E10" t="n">
-        <v>1.245481124226629</v>
+        <v>1.245199550529824</v>
       </c>
     </row>
     <row r="11">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.215256687984137</v>
+        <v>-1.21649126198373</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4727189147082672</v>
+        <v>0.4734587680134759</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3442752192837136</v>
+        <v>-0.3426045615969134</v>
       </c>
       <c r="E11" t="n">
-        <v>1.086812992559584</v>
+        <v>1.085637055567168</v>
       </c>
     </row>
     <row r="12">
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.192909502809954</v>
+        <v>1.192541106795055</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4474884185774866</v>
+        <v>0.4486838786717254</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9452354555504406</v>
+        <v>-0.9425113161105</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6951624658370011</v>
+        <v>-0.6987136693562777</v>
       </c>
     </row>
     <row r="13">
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1134718933334722</v>
+        <v>-0.113550334224299</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.5778283126881167</v>
+        <v>-0.5778155155900307</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.753051509856179</v>
+        <v>-0.7530076747597677</v>
       </c>
       <c r="E13" t="n">
-        <v>1.444351715877767</v>
+        <v>1.444373524574098</v>
       </c>
     </row>
     <row r="14">
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.01197225555019891</v>
+        <v>-0.01183869815486567</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2951487624300236</v>
+        <v>-0.2950942904805482</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.043431973480892</v>
+        <v>-1.043545424595945</v>
       </c>
       <c r="E14" t="n">
-        <v>1.350552991461112</v>
+        <v>1.35047841323136</v>
       </c>
     </row>
     <row r="15">
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.8716048244405507</v>
+        <v>-0.8720617300453677</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.6382506229445036</v>
+        <v>-0.6379817186788262</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1662387579376451</v>
+        <v>0.1666459865987931</v>
       </c>
       <c r="E15" t="n">
-        <v>1.34361668944741</v>
+        <v>1.343397462125401</v>
       </c>
     </row>
   </sheetData>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3166251379475805</v>
+        <v>0.3118264606236348</v>
       </c>
     </row>
     <row r="3">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2964011259524472</v>
+        <v>0.2992114619675032</v>
       </c>
     </row>
     <row r="4">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.0515857108037336</v>
+        <v>0.05382509633316336</v>
       </c>
     </row>
     <row r="5">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.09873136232283775</v>
+        <v>0.09352730933122236</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6365187190706765</v>
+        <v>0.6377746166384903</v>
       </c>
     </row>
     <row r="7">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.712475726462932</v>
+        <v>0.712339018441777</v>
       </c>
     </row>
     <row r="8">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3648057205123224</v>
+        <v>0.3648944832489373</v>
       </c>
     </row>
     <row r="9">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.6278219309276203</v>
+        <v>0.6262508559138069</v>
       </c>
     </row>
     <row r="24">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.6685968363322742</v>
+        <v>0.6712400154391471</v>
       </c>
     </row>
     <row r="25">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.4382506811295231</v>
+        <v>0.4211459494006819</v>
       </c>
     </row>
     <row r="26">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.3177765737030471</v>
+        <v>0.2195376791941058</v>
       </c>
     </row>
     <row r="27">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.6223366485352284</v>
+        <v>0.6255097451330235</v>
       </c>
     </row>
     <row r="28">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.7403120205767268</v>
+        <v>0.7404981213895235</v>
       </c>
     </row>
     <row r="29">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.09153553215716577</v>
+        <v>0.09004869385205888</v>
       </c>
     </row>
   </sheetData>
@@ -1336,7 +1336,7 @@
         <v>0.4398826979472141</v>
       </c>
       <c r="D2" t="n">
-        <v>2669</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="3">
@@ -1384,7 +1384,7 @@
         <v>0.155425219941349</v>
       </c>
       <c r="D5" t="n">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
   </sheetData>

--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV16_regime_templates_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV16_regime_templates_data.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-57bdbc83894f</t>
+          <t>d1-final-ab36d51d4f60</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,16 +498,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.334969113657857</v>
+        <v>1.335053832194183</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1771281425030413</v>
+        <v>0.17694629510425</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9030920280545595</v>
+        <v>-0.9030180508907029</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6090052281063398</v>
+        <v>-0.6089820764077308</v>
       </c>
     </row>
     <row r="3">
@@ -517,16 +517,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.42233930465182</v>
+        <v>1.422316054688259</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.02908114856459194</v>
+        <v>-0.02901362204470088</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.644170259866192</v>
+        <v>-0.6441525802459185</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.7490878962210363</v>
+        <v>-0.7491498523976394</v>
       </c>
     </row>
     <row r="4">
@@ -536,16 +536,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6325744471908278</v>
+        <v>0.6320887357930685</v>
       </c>
       <c r="C4" t="n">
-        <v>1.063835444743421</v>
+        <v>1.064216775145813</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9690173657198674</v>
+        <v>-0.9689234524933621</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7273925262143814</v>
+        <v>-0.7273820584455201</v>
       </c>
     </row>
     <row r="5">
@@ -555,16 +555,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1980647397956018</v>
+        <v>-0.1967324031430473</v>
       </c>
       <c r="C5" t="n">
-        <v>1.450795803592178</v>
+        <v>1.450553449104566</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4383851538956044</v>
+        <v>-0.439111490324021</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8143459099009709</v>
+        <v>-0.8147095556374967</v>
       </c>
     </row>
     <row r="6">
@@ -574,16 +574,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5864695142181653</v>
+        <v>0.5860385782126571</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.7599771007230918</v>
+        <v>-0.7597772541494865</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9289772284038152</v>
+        <v>-0.9290509061337016</v>
       </c>
       <c r="E6" t="n">
-        <v>1.102484814908742</v>
+        <v>1.102789582070532</v>
       </c>
     </row>
     <row r="7">
@@ -593,16 +593,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.04386616431932</v>
+        <v>1.043763123377636</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.086602970952858</v>
+        <v>-1.086743296914492</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5822427827427386</v>
+        <v>-0.5820795587858147</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6249795893762748</v>
+        <v>0.6250597323226736</v>
       </c>
     </row>
     <row r="8">
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7421978440480835</v>
+        <v>0.7413462001126273</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6614489719394756</v>
+        <v>0.662429068942841</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.418241755263595</v>
+        <v>-1.418231165426848</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01459493927603462</v>
+        <v>0.01445589637137852</v>
       </c>
     </row>
     <row r="9">
@@ -631,16 +631,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.8749464036495195</v>
+        <v>-0.8747458893114542</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.2403154172827242</v>
+        <v>-0.2398361309344532</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3240604794323711</v>
+        <v>-0.3247799292607327</v>
       </c>
       <c r="E9" t="n">
-        <v>1.439322300364614</v>
+        <v>1.439361949506641</v>
       </c>
     </row>
     <row r="10">
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.167279247796931</v>
+        <v>-1.168182308930083</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1658584411076214</v>
+        <v>0.1659726250487227</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2437787438405123</v>
+        <v>-0.2423973158236088</v>
       </c>
       <c r="E10" t="n">
-        <v>1.245199550529824</v>
+        <v>1.24460699970497</v>
       </c>
     </row>
     <row r="11">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-1.21649126198373</v>
+        <v>-1.216967281371976</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4734587680134759</v>
+        <v>0.4732667445731052</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3426045615969134</v>
+        <v>-0.3417546215596395</v>
       </c>
       <c r="E11" t="n">
-        <v>1.085637055567168</v>
+        <v>1.085455158358511</v>
       </c>
     </row>
     <row r="12">
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.192541106795055</v>
+        <v>1.192906098601041</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4486838786717254</v>
+        <v>0.4480686572350659</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9425113161105</v>
+        <v>-0.9425740901800161</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6987136693562777</v>
+        <v>-0.69840066565609</v>
       </c>
     </row>
     <row r="13">
@@ -707,16 +707,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.113550334224299</v>
+        <v>-0.1145173842571225</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.5778155155900307</v>
+        <v>-0.5779683471376803</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.7530076747597677</v>
+        <v>-0.7521810050241329</v>
       </c>
       <c r="E13" t="n">
-        <v>1.444373524574098</v>
+        <v>1.444666736418935</v>
       </c>
     </row>
     <row r="14">
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.01183869815486567</v>
+        <v>-0.01192352161782237</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.2950942904805482</v>
+        <v>-0.2955857009633376</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.043545424595945</v>
+        <v>-1.043159285966906</v>
       </c>
       <c r="E14" t="n">
-        <v>1.35047841323136</v>
+        <v>1.350668508548068</v>
       </c>
     </row>
     <row r="15">
@@ -745,16 +745,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.8720617300453677</v>
+        <v>-0.8722474201180478</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.6379817186788262</v>
+        <v>-0.6381213570843419</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1666459865987931</v>
+        <v>0.1672308995150024</v>
       </c>
       <c r="E15" t="n">
-        <v>1.343397462125401</v>
+        <v>1.343137877687388</v>
       </c>
     </row>
   </sheetData>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3118264606236348</v>
+        <v>0.3090353532362588</v>
       </c>
     </row>
     <row r="3">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.2992114619675032</v>
+        <v>0.2992249952303511</v>
       </c>
     </row>
     <row r="4">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05382509633316336</v>
+        <v>0.05546793573992796</v>
       </c>
     </row>
     <row r="5">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.09352730933122236</v>
+        <v>0.09332721888232483</v>
       </c>
     </row>
     <row r="6">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6377746166384903</v>
+        <v>0.6320075254130312</v>
       </c>
     </row>
     <row r="7">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.712339018441777</v>
+        <v>0.7112425741349782</v>
       </c>
     </row>
     <row r="8">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3648944832489373</v>
+        <v>0.3625347362347931</v>
       </c>
     </row>
     <row r="9">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.1268071283446265</v>
+        <v>-0.1267975883359024</v>
       </c>
     </row>
     <row r="10">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3726115839043568</v>
+        <v>0.3725404341219131</v>
       </c>
     </row>
     <row r="11">
@@ -965,7 +965,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3153034434400146</v>
+        <v>0.3130957424329421</v>
       </c>
     </row>
     <row r="12">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.06605526679075389</v>
+        <v>0.06590257370945482</v>
       </c>
     </row>
     <row r="13">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1512283237904969</v>
+        <v>0.1503924174767793</v>
       </c>
     </row>
     <row r="14">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.8247511452963079</v>
+        <v>0.8247007226620015</v>
       </c>
     </row>
     <row r="15">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4039858676734722</v>
+        <v>0.4031434321905919</v>
       </c>
     </row>
     <row r="16">
@@ -1336,7 +1336,7 @@
         <v>0.4398826979472141</v>
       </c>
       <c r="D2" t="n">
-        <v>2691</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="3">
@@ -1352,7 +1352,7 @@
         <v>0.2378624959270121</v>
       </c>
       <c r="D3" t="n">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="4">
